--- a/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
+++ b/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Record</t>
   </si>
@@ -30,184 +30,166 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Knee Chubbs 401(k)</t>
+  </si>
+  <si>
+    <t>Chum is Fum</t>
+  </si>
+  <si>
     <t>Bands Emeka Dance</t>
   </si>
   <si>
-    <t>Knee Chubbs 401(k)</t>
-  </si>
-  <si>
-    <t>Chum is Fum</t>
-  </si>
-  <si>
     <t>Rocket Bowers</t>
   </si>
   <si>
+    <t>Revenge of De Smithy</t>
+  </si>
+  <si>
+    <t>Infinite Blitz</t>
+  </si>
+  <si>
+    <t>Rice Rice Baby</t>
+  </si>
+  <si>
+    <t>Delco Football Team</t>
+  </si>
+  <si>
     <t>Fiery Dragons</t>
   </si>
   <si>
-    <t>Revenge of De Smithy</t>
-  </si>
-  <si>
-    <t>Delco Football Team</t>
-  </si>
-  <si>
-    <t>Rice Rice Baby</t>
-  </si>
-  <si>
-    <t>Infinite Blitz</t>
-  </si>
-  <si>
     <t>Wookie Warriors</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>97.2%</t>
-  </si>
-  <si>
-    <t>92.2%</t>
-  </si>
-  <si>
-    <t>72.8%</t>
-  </si>
-  <si>
-    <t>51.2%</t>
-  </si>
-  <si>
-    <t>47.3%</t>
-  </si>
-  <si>
-    <t>26.6%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>99.5%</t>
+  </si>
+  <si>
+    <t>96.9%</t>
+  </si>
+  <si>
+    <t>74.2%</t>
+  </si>
+  <si>
+    <t>48.5%</t>
+  </si>
+  <si>
+    <t>34.8%</t>
+  </si>
+  <si>
+    <t>31.7%</t>
+  </si>
+  <si>
+    <t>14.8%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-3471</t>
-  </si>
-  <si>
-    <t>-1182</t>
-  </si>
-  <si>
-    <t>-268</t>
-  </si>
-  <si>
-    <t>-105</t>
-  </si>
-  <si>
-    <t>+111</t>
-  </si>
-  <si>
-    <t>+276</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+2464</t>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-3126</t>
+  </si>
+  <si>
+    <t>-288</t>
+  </si>
+  <si>
+    <t>+106</t>
+  </si>
+  <si>
+    <t>+187</t>
+  </si>
+  <si>
+    <t>+215</t>
+  </si>
+  <si>
+    <t>+576</t>
+  </si>
+  <si>
+    <t>+99900</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>45.2%</t>
-  </si>
-  <si>
-    <t>37.7%</t>
-  </si>
-  <si>
-    <t>14.8%</t>
+    <t>69.7%</t>
+  </si>
+  <si>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-230</t>
+  </si>
+  <si>
+    <t>+446</t>
+  </si>
+  <si>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>+3233</t>
+  </si>
+  <si>
+    <t>89.6%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
   </si>
   <si>
     <t>1.8%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+121</t>
-  </si>
-  <si>
-    <t>+165</t>
-  </si>
-  <si>
-    <t>+576</t>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-862</t>
+  </si>
+  <si>
+    <t>+1983</t>
+  </si>
+  <si>
+    <t>+4445</t>
   </si>
   <si>
     <t>+5456</t>
   </si>
   <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>55.8%</t>
-  </si>
-  <si>
-    <t>26.8%</t>
-  </si>
-  <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>3.7%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-126</t>
-  </si>
-  <si>
-    <t>+273</t>
-  </si>
-  <si>
-    <t>+1415</t>
-  </si>
-  <si>
-    <t>+2281</t>
-  </si>
-  <si>
-    <t>+2603</t>
-  </si>
-  <si>
-    <t>+3746</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
 </sst>
 </file>
@@ -590,7 +572,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -601,10 +583,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -615,13 +597,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -635,7 +617,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -643,13 +625,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -663,7 +645,7 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -677,7 +659,7 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -685,13 +667,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,7 +687,7 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -713,13 +695,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -740,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -754,10 +736,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -765,13 +747,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -779,13 +761,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -796,10 +778,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -807,27 +789,27 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -835,55 +817,55 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -915,13 +897,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -932,10 +914,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -943,41 +925,41 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -985,69 +967,69 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
+++ b/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
@@ -33,163 +33,163 @@
     <t>Knee Chubbs 401(k)</t>
   </si>
   <si>
+    <t>Bands Emeka Dance</t>
+  </si>
+  <si>
+    <t>Rocket Bowers</t>
+  </si>
+  <si>
     <t>Chum is Fum</t>
   </si>
   <si>
-    <t>Bands Emeka Dance</t>
-  </si>
-  <si>
-    <t>Rocket Bowers</t>
+    <t>Rice Rice Baby</t>
+  </si>
+  <si>
+    <t>Delco Football Team</t>
+  </si>
+  <si>
+    <t>Infinite Blitz</t>
   </si>
   <si>
     <t>Revenge of De Smithy</t>
   </si>
   <si>
-    <t>Infinite Blitz</t>
-  </si>
-  <si>
-    <t>Rice Rice Baby</t>
-  </si>
-  <si>
-    <t>Delco Football Team</t>
-  </si>
-  <si>
     <t>Fiery Dragons</t>
   </si>
   <si>
     <t>Wookie Warriors</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>96.9%</t>
-  </si>
-  <si>
-    <t>74.2%</t>
-  </si>
-  <si>
-    <t>48.5%</t>
-  </si>
-  <si>
-    <t>34.8%</t>
-  </si>
-  <si>
-    <t>31.7%</t>
-  </si>
-  <si>
-    <t>14.8%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>98.3%</t>
+  </si>
+  <si>
+    <t>88.6%</t>
+  </si>
+  <si>
+    <t>61.1%</t>
+  </si>
+  <si>
+    <t>23.8%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-5782</t>
+  </si>
+  <si>
+    <t>-777</t>
+  </si>
+  <si>
+    <t>-157</t>
+  </si>
+  <si>
+    <t>+320</t>
+  </si>
+  <si>
+    <t>+521</t>
+  </si>
+  <si>
+    <t>+700</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>80.8%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-421</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+1438</t>
+  </si>
+  <si>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>92.1%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-3126</t>
-  </si>
-  <si>
-    <t>-288</t>
-  </si>
-  <si>
-    <t>+106</t>
-  </si>
-  <si>
-    <t>+187</t>
-  </si>
-  <si>
-    <t>+215</t>
-  </si>
-  <si>
-    <t>+576</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>69.7%</t>
-  </si>
-  <si>
-    <t>18.3%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-230</t>
-  </si>
-  <si>
-    <t>+446</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
-    <t>+3233</t>
-  </si>
-  <si>
-    <t>89.6%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>-862</t>
-  </si>
-  <si>
-    <t>+1983</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>-1166</t>
+  </si>
+  <si>
+    <t>+3348</t>
+  </si>
+  <si>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>+4662</t>
   </si>
 </sst>
 </file>
@@ -572,10 +572,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -586,10 +586,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,10 +600,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,13 +611,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -625,13 +625,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -642,10 +642,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -653,13 +653,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -667,13 +667,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -681,13 +681,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -695,13 +695,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -736,10 +736,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -750,10 +750,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -764,10 +764,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -775,13 +775,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -789,55 +789,55 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -845,27 +845,27 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -897,139 +897,139 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
+++ b/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
   <si>
     <t>Record</t>
   </si>
@@ -33,100 +33,103 @@
     <t>Knee Chubbs 401(k)</t>
   </si>
   <si>
+    <t>Chum is Fum</t>
+  </si>
+  <si>
     <t>Bands Emeka Dance</t>
   </si>
   <si>
     <t>Rocket Bowers</t>
   </si>
   <si>
-    <t>Chum is Fum</t>
-  </si>
-  <si>
     <t>Rice Rice Baby</t>
   </si>
   <si>
     <t>Delco Football Team</t>
   </si>
   <si>
+    <t>Revenge of De Smithy</t>
+  </si>
+  <si>
+    <t>Fiery Dragons</t>
+  </si>
+  <si>
     <t>Infinite Blitz</t>
   </si>
   <si>
-    <t>Revenge of De Smithy</t>
-  </si>
-  <si>
-    <t>Fiery Dragons</t>
-  </si>
-  <si>
     <t>Wookie Warriors</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>98.3%</t>
-  </si>
-  <si>
-    <t>88.6%</t>
-  </si>
-  <si>
-    <t>61.1%</t>
-  </si>
-  <si>
-    <t>23.8%</t>
-  </si>
-  <si>
-    <t>16.1%</t>
-  </si>
-  <si>
-    <t>12.5%</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>96.9%</t>
+  </si>
+  <si>
+    <t>96.5%</t>
+  </si>
+  <si>
+    <t>92.0%</t>
+  </si>
+  <si>
+    <t>90.9%</t>
+  </si>
+  <si>
+    <t>73.7%</t>
+  </si>
+  <si>
+    <t>36.0%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-5782</t>
-  </si>
-  <si>
-    <t>-777</t>
-  </si>
-  <si>
-    <t>-157</t>
-  </si>
-  <si>
-    <t>+320</t>
-  </si>
-  <si>
-    <t>+521</t>
-  </si>
-  <si>
-    <t>+700</t>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-3126</t>
+  </si>
+  <si>
+    <t>-2757</t>
+  </si>
+  <si>
+    <t>-1150</t>
+  </si>
+  <si>
+    <t>-999</t>
+  </si>
+  <si>
+    <t>-280</t>
+  </si>
+  <si>
+    <t>+178</t>
+  </si>
+  <si>
+    <t>+635</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
   <si>
     <t>+99900</t>
@@ -135,61 +138,61 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>80.8%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>6.5%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-421</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+1438</t>
-  </si>
-  <si>
-    <t>+3604</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>92.1%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
+    <t>64.7%</t>
+  </si>
+  <si>
+    <t>13.4%</t>
+  </si>
+  <si>
+    <t>12.2%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>-183</t>
+  </si>
+  <si>
+    <t>+646</t>
+  </si>
+  <si>
+    <t>+720</t>
+  </si>
+  <si>
+    <t>+1983</t>
+  </si>
+  <si>
+    <t>+2678</t>
+  </si>
+  <si>
+    <t>+7592</t>
+  </si>
+  <si>
+    <t>93.1%</t>
+  </si>
+  <si>
+    <t>6.2%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>-1166</t>
-  </si>
-  <si>
-    <t>+3348</t>
-  </si>
-  <si>
-    <t>+3471</t>
-  </si>
-  <si>
-    <t>+4662</t>
+    <t>-1349</t>
+  </si>
+  <si>
+    <t>+1513</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
 </sst>
 </file>
@@ -589,7 +592,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -597,13 +600,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,13 +614,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -625,13 +628,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -639,13 +642,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -653,13 +656,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -673,7 +676,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -687,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -701,7 +704,7 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -722,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -736,99 +739,99 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -837,35 +840,35 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -900,38 +903,38 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -939,13 +942,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -953,27 +956,27 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -987,12 +990,12 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -1001,21 +1004,21 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1023,13 +1026,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
+++ b/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Record</t>
   </si>
@@ -30,24 +30,24 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Chum is Fum</t>
+  </si>
+  <si>
     <t>Knee Chubbs 401(k)</t>
   </si>
   <si>
-    <t>Chum is Fum</t>
-  </si>
-  <si>
     <t>Bands Emeka Dance</t>
   </si>
   <si>
+    <t>Delco Football Team</t>
+  </si>
+  <si>
     <t>Rocket Bowers</t>
   </si>
   <si>
     <t>Rice Rice Baby</t>
   </si>
   <si>
-    <t>Delco Football Team</t>
-  </si>
-  <si>
     <t>Revenge of De Smithy</t>
   </si>
   <si>
@@ -60,76 +60,70 @@
     <t>Wookie Warriors</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>99.6%</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>99.0%</t>
+  </si>
+  <si>
+    <t>98.8%</t>
   </si>
   <si>
     <t>96.9%</t>
   </si>
   <si>
-    <t>96.5%</t>
-  </si>
-  <si>
-    <t>92.0%</t>
-  </si>
-  <si>
-    <t>90.9%</t>
-  </si>
-  <si>
-    <t>73.7%</t>
-  </si>
-  <si>
-    <t>36.0%</t>
-  </si>
-  <si>
-    <t>13.6%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
+    <t>96.7%</t>
+  </si>
+  <si>
+    <t>95.1%</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>48.8%</t>
+  </si>
+  <si>
+    <t>4.1%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-24900</t>
+    <t>-9900</t>
+  </si>
+  <si>
+    <t>-8233</t>
   </si>
   <si>
     <t>-3126</t>
   </si>
   <si>
-    <t>-2757</t>
-  </si>
-  <si>
-    <t>-1150</t>
-  </si>
-  <si>
-    <t>-999</t>
-  </si>
-  <si>
-    <t>-280</t>
-  </si>
-  <si>
-    <t>+178</t>
-  </si>
-  <si>
-    <t>+635</t>
-  </si>
-  <si>
-    <t>+12400</t>
+    <t>-2930</t>
+  </si>
+  <si>
+    <t>-1941</t>
+  </si>
+  <si>
+    <t>-150</t>
+  </si>
+  <si>
+    <t>+105</t>
+  </si>
+  <si>
+    <t>+2339</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
   <si>
     <t>+99900</t>
@@ -138,61 +132,64 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>64.7%</t>
-  </si>
-  <si>
-    <t>13.4%</t>
-  </si>
-  <si>
-    <t>12.2%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
-  </si>
-  <si>
-    <t>-183</t>
-  </si>
-  <si>
-    <t>+646</t>
-  </si>
-  <si>
-    <t>+720</t>
-  </si>
-  <si>
-    <t>+1983</t>
-  </si>
-  <si>
-    <t>+2678</t>
-  </si>
-  <si>
-    <t>+7592</t>
-  </si>
-  <si>
-    <t>93.1%</t>
-  </si>
-  <si>
-    <t>6.2%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-1349</t>
-  </si>
-  <si>
-    <t>+1513</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>32.8%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>14.6%</t>
+  </si>
+  <si>
+    <t>11.6%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>+205</t>
+  </si>
+  <si>
+    <t>+229</t>
+  </si>
+  <si>
+    <t>+585</t>
+  </si>
+  <si>
+    <t>+762</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>71.9%</t>
+  </si>
+  <si>
+    <t>23.0%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>-256</t>
+  </si>
+  <si>
+    <t>+335</t>
+  </si>
+  <si>
+    <t>+1861</t>
   </si>
 </sst>
 </file>
@@ -575,10 +572,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -586,13 +583,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -603,10 +600,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -614,13 +611,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -631,10 +628,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -642,13 +639,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -656,13 +653,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -670,13 +667,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -684,13 +681,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -698,13 +695,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -739,66 +736,66 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -806,55 +803,55 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -862,13 +859,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -900,13 +897,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -914,13 +911,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -928,83 +925,83 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1015,24 +1012,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
+++ b/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
   <si>
     <t>Record</t>
   </si>
@@ -39,12 +39,12 @@
     <t>Bands Emeka Dance</t>
   </si>
   <si>
+    <t>Rocket Bowers</t>
+  </si>
+  <si>
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>Rocket Bowers</t>
-  </si>
-  <si>
     <t>Rice Rice Baby</t>
   </si>
   <si>
@@ -60,70 +60,73 @@
     <t>Wookie Warriors</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>99.0%</t>
-  </si>
-  <si>
-    <t>98.8%</t>
-  </si>
-  <si>
-    <t>96.9%</t>
-  </si>
-  <si>
-    <t>96.7%</t>
-  </si>
-  <si>
-    <t>95.1%</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>48.8%</t>
-  </si>
-  <si>
-    <t>4.1%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>97.1%</t>
+  </si>
+  <si>
+    <t>94.6%</t>
+  </si>
+  <si>
+    <t>89.0%</t>
+  </si>
+  <si>
+    <t>60.2%</t>
+  </si>
+  <si>
+    <t>56.7%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-9900</t>
-  </si>
-  <si>
-    <t>-8233</t>
-  </si>
-  <si>
-    <t>-3126</t>
-  </si>
-  <si>
-    <t>-2930</t>
-  </si>
-  <si>
-    <t>-1941</t>
-  </si>
-  <si>
-    <t>-150</t>
-  </si>
-  <si>
-    <t>+105</t>
-  </si>
-  <si>
-    <t>+2339</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-3348</t>
+  </si>
+  <si>
+    <t>-1752</t>
+  </si>
+  <si>
+    <t>-809</t>
+  </si>
+  <si>
+    <t>-151</t>
+  </si>
+  <si>
+    <t>-131</t>
+  </si>
+  <si>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+8991</t>
   </si>
   <si>
     <t>+99900</t>
@@ -132,64 +135,58 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>32.8%</t>
-  </si>
-  <si>
-    <t>30.4%</t>
-  </si>
-  <si>
-    <t>14.6%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
+    <t>42.3%</t>
+  </si>
+  <si>
+    <t>40.4%</t>
+  </si>
+  <si>
+    <t>11.4%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>+205</t>
-  </si>
-  <si>
-    <t>+229</t>
-  </si>
-  <si>
-    <t>+585</t>
-  </si>
-  <si>
-    <t>+762</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+8233</t>
+    <t>+136</t>
+  </si>
+  <si>
+    <t>+148</t>
+  </si>
+  <si>
+    <t>+777</t>
+  </si>
+  <si>
+    <t>+2603</t>
+  </si>
+  <si>
+    <t>+5456</t>
   </si>
   <si>
     <t>+49900</t>
   </si>
   <si>
-    <t>71.9%</t>
-  </si>
-  <si>
-    <t>23.0%</t>
-  </si>
-  <si>
-    <t>5.1%</t>
-  </si>
-  <si>
-    <t>-256</t>
-  </si>
-  <si>
-    <t>+335</t>
-  </si>
-  <si>
-    <t>+1861</t>
+    <t>92.1%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>-1166</t>
+  </si>
+  <si>
+    <t>+2400</t>
+  </si>
+  <si>
+    <t>+2464</t>
   </si>
 </sst>
 </file>
@@ -572,10 +569,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -586,10 +583,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,10 +597,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,13 +608,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -625,13 +622,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -639,13 +636,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -656,10 +653,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -670,10 +667,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -681,13 +678,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -698,10 +695,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -722,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -736,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>45</v>
@@ -750,7 +747,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
@@ -764,7 +761,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>47</v>
@@ -775,10 +772,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>48</v>
@@ -789,10 +786,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>49</v>
@@ -803,10 +800,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>50</v>
@@ -823,7 +820,7 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -834,10 +831,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -845,13 +842,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -862,10 +859,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -900,38 +897,38 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -939,13 +936,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -956,10 +953,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -970,10 +967,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -984,24 +981,24 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1012,24 +1009,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
+++ b/data/odds/The Goofy Goobers 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="54">
   <si>
     <t>Record</t>
   </si>
@@ -30,12 +30,12 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Knee Chubbs 401(k)</t>
+  </si>
+  <si>
     <t>Chum is Fum</t>
   </si>
   <si>
-    <t>Knee Chubbs 401(k)</t>
-  </si>
-  <si>
     <t>Bands Emeka Dance</t>
   </si>
   <si>
@@ -45,12 +45,12 @@
     <t>Delco Football Team</t>
   </si>
   <si>
+    <t>Revenge of De Smithy</t>
+  </si>
+  <si>
     <t>Rice Rice Baby</t>
   </si>
   <si>
-    <t>Revenge of De Smithy</t>
-  </si>
-  <si>
     <t>Fiery Dragons</t>
   </si>
   <si>
@@ -75,28 +75,28 @@
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>97.1%</t>
-  </si>
-  <si>
-    <t>94.6%</t>
-  </si>
-  <si>
-    <t>89.0%</t>
-  </si>
-  <si>
-    <t>60.2%</t>
-  </si>
-  <si>
-    <t>56.7%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>98.0%</t>
+  </si>
+  <si>
+    <t>94.9%</t>
+  </si>
+  <si>
+    <t>89.4%</t>
+  </si>
+  <si>
+    <t>58.2%</t>
+  </si>
+  <si>
+    <t>57.8%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.0%</t>
@@ -105,28 +105,25 @@
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-3348</t>
-  </si>
-  <si>
-    <t>-1752</t>
-  </si>
-  <si>
-    <t>-809</t>
-  </si>
-  <si>
-    <t>-151</t>
-  </si>
-  <si>
-    <t>-131</t>
-  </si>
-  <si>
-    <t>+6567</t>
-  </si>
-  <si>
-    <t>+8991</t>
+    <t>-4900</t>
+  </si>
+  <si>
+    <t>-1861</t>
+  </si>
+  <si>
+    <t>-843</t>
+  </si>
+  <si>
+    <t>-139</t>
+  </si>
+  <si>
+    <t>-137</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
   <si>
     <t>+99900</t>
@@ -135,58 +132,52 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>42.3%</t>
-  </si>
-  <si>
-    <t>40.4%</t>
-  </si>
-  <si>
-    <t>11.4%</t>
-  </si>
-  <si>
-    <t>3.7%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>43.4%</t>
+  </si>
+  <si>
+    <t>42.4%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>+130</t>
   </si>
   <si>
     <t>+136</t>
   </si>
   <si>
-    <t>+148</t>
-  </si>
-  <si>
-    <t>+777</t>
-  </si>
-  <si>
-    <t>+2603</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>92.1%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>-1166</t>
+    <t>+1076</t>
   </si>
   <si>
     <t>+2400</t>
   </si>
   <si>
-    <t>+2464</t>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>91.6%</t>
+  </si>
+  <si>
+    <t>5.2%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>-1090</t>
+  </si>
+  <si>
+    <t>+1823</t>
+  </si>
+  <si>
+    <t>+3025</t>
   </si>
 </sst>
 </file>
@@ -586,7 +577,7 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,7 +591,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -614,7 +605,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -628,7 +619,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -642,7 +633,7 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -656,7 +647,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -670,7 +661,7 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -684,7 +675,7 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -698,7 +689,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -727,30 +718,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -761,10 +752,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -775,10 +766,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -789,10 +780,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -803,10 +794,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -817,10 +808,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -834,7 +825,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -848,7 +839,7 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -862,7 +853,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -897,10 +888,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -911,10 +902,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
         <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -925,15 +916,15 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
         <v>53</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -942,12 +933,12 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -956,12 +947,12 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -970,12 +961,12 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -984,7 +975,7 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -998,7 +989,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1012,7 +1003,7 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1026,7 +1017,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
